--- a/Xlsx/Example/Record.xlsx
+++ b/Xlsx/Example/Record.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19095" windowHeight="12585"/>
+    <workbookView windowWidth="27945" windowHeight="14055"/>
   </bookViews>
   <sheets>
     <sheet name="record_1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t>Id</t>
   </si>
@@ -70,13 +83,10 @@
     <t>UserData</t>
   </si>
   <si>
-    <t>object</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Int</t>
   </si>
   <si>
     <t>Desc</t>
@@ -91,18 +101,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -113,53 +123,25 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -167,14 +149,15 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -182,89 +165,109 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,25 +294,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,157 +432,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,32 +512,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -564,16 +546,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -588,6 +570,21 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -617,148 +614,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -775,9 +772,15 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -787,63 +790,57 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1113,13 +1110,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultColWidth="8.72592592592593" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.9037037037037" customWidth="1"/>
-    <col min="2" max="2" width="24.7259259259259" customWidth="1"/>
-    <col min="3" max="3" width="23.0888888888889" customWidth="1"/>
-    <col min="4" max="4" width="26.0888888888889" customWidth="1"/>
-    <col min="5" max="5" width="19.7259259259259" customWidth="1"/>
+    <col min="1" max="1" width="13.9" customWidth="1"/>
+    <col min="2" max="2" width="24.725" customWidth="1"/>
+    <col min="3" max="3" width="23.0916666666667" customWidth="1"/>
+    <col min="4" max="4" width="26.0916666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.725" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:14">
@@ -1133,291 +1130,294 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:14">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>256</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:14">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:14">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:14">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="H5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="M5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>19</v>
+      <c r="N5" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:14">
-      <c r="A6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
+      <c r="A6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:14">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:14">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>512</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:14">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>2</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:14">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="B10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:14">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:14">
-      <c r="A12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="A12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B3 A8:B9">
-      <formula1>0</formula1>
+  <dataValidations count="5">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="A4:B4 D6:F6 A10:B10 E1:F3">
+      <formula1>"int,string,float,object"</formula1>
+    </dataValidation>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="C4:N4"/>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="A5:C5 H5:K5 N5">
+      <formula1>"Int,String,Float,Object"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 C1:D3">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D5 E5 F5 D6 E6 F6 A4:A5 B4:B5 E1:E3 F1:F3 A10:B11">
-      <formula1>"int,string,float,object"</formula1>
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B3 A8:B9">
+      <formula1>0</formula1>
     </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="D4 E4 F4 G4 H4 I4 J4 K4 L4 M4 N4 H5 I5 J5 K5 L5 M5 N5 C4:C5"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
